--- a/erp-server/erp-server-file/src/main/resources/excel/wms/unPackingDetailExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/unPackingDetailExport.xlsx
@@ -61,7 +61,7 @@
     <t>{.sourceCode}</t>
   </si>
   <si>
-    <t>{.sku}</t>
+    <t>{.skuNo}</t>
   </si>
   <si>
     <t>{.fnSku}</t>
